--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeLine001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeLine001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace_BS_2.1.2.SNS-TZJY-V1\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7860"/>
+    <workbookView windowWidth="29340" windowHeight="12840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="230">
   <si>
     <t>额度分类</t>
   </si>
@@ -31,13 +26,7 @@
     <t>扣减规则</t>
   </si>
   <si>
-    <t>是否永续债</t>
-  </si>
-  <si>
-    <t>发行方式</t>
-  </si>
-  <si>
-    <t>期限</t>
+    <t>风险系数(%)</t>
   </si>
   <si>
     <t>AUD/CAD:AUD/CAD</t>
@@ -716,21 +705,19 @@
   </si>
   <si>
     <t>USD/TWD:USD/TWD</t>
-  </si>
-  <si>
-    <t>风险系数(%)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>期限单位</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,37 +728,353 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -794,33 +1097,319 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2 2" xfId="1"/>
-    <cellStyle name="常规 3" xfId="2"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="常规 2 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="31" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="32" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="33" builtinId="9"/>
+    <cellStyle name="标题" xfId="34" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="35" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="36" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="37" builtinId="40"/>
+    <cellStyle name="注释" xfId="38" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="39" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="40" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="41" builtinId="51"/>
+    <cellStyle name="超链接" xfId="42" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="43" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="44" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="46" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="47" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="48" builtinId="31"/>
+    <cellStyle name="常规 3" xfId="49"/>
+    <cellStyle name="链接单元格" xfId="50" builtinId="24"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1078,23 +1667,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="18.375" customWidth="1"/>
     <col min="3" max="3" width="16.125" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="11.75" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="15" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1104,1188 +1691,1168 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>232</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>"01:资金类额度,02:债券投资类额度,03:次级债务额度,04:无固定期限资本补充工具,05:信用债质押专项额度,06:受益权,07:交易类额度,08:企业信用债投资额度,09:北金所债权融资计划额度,10:同业ABS投资限额,11:CB/EB专项额度,12:不扣限额"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 C1 D1 E1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>"01:公开发行,02:非公开发行"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"01:名义本金,02:净值型资产-金额,03:净值型资产-份额"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"Y:是,N:否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
-      <formula1>"日,月,周,年"</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 C1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A226"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>